--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-07-2025.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£12.12</t>
+          <t>£11.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>£13.33</t>
+          <t>£13.68</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£18.00</t>
+          <t>£15.55</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£17.48</t>
+          <t>£17.88</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>£24.48</t>
+          <t>£21.00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£24.68</t>
+          <t>£24.75</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£25.00</t>
+          <t>£25.48</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>£27.62</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1314,37 +1314,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://insulation4less.co.uk/products/90mm-celotex-ga3090-2-4m-x-1-2m</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>£29.28</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>£29.28</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>£32.00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>£29.28</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>£32.00</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>£29.28</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>£29.28</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£31.00</t>
+          <t>£28.58</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£31.00</t>
+          <t>£31.62</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£41.18</t>
+          <t>£37.14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£38.00</t>
+          <t>£36.88</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£46.88</t>
+          <t>£51.88</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£48.99</t>
+          <t>£42.48</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>£768.0</t>
+          <t>£181.56</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>£984.0</t>
+          <t>£81.96</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>£33.33</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>£40.00</t>
+          <t>£18.08</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>£46.00</t>
+          <t>£25.48</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>£53.33</t>
+          <t>£10.08</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>£58.00</t>
+          <t>£5.27</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>£61.00</t>
+          <t>£7.63</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>£58.00</t>
+          <t>£9.67</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>£1424.0</t>
+          <t>£237.28</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>£1504.0</t>
+          <t>£300.8</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
